--- a/stories/arbres/TREE-JEU-005.xlsx
+++ b/stories/arbres/TREE-JEU-005.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Nora est dans le train, avec papa. Un petit jeu de cartes épaisses. Papa dit une règle : on attend, puis on pose une carte. Une règle. Nora attend. Nora pose. Papa la rappelle une fois, tout doux. Rappeler. Une règle. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1653,6 +1680,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pense au bac à sable. La règle : on reste assis dans le train. Une règle. Papa la rappelle. Nora suit la règle dite. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1865,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|On suit une quoi ?</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2038,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Nora a suivi une règle. Papa a pu la rappeler. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2233,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2400,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend les cubes. La corde du sac est rêche. Les cubes : une règle, un cube à la fois. Papa la rappelle. Nora suit. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2541,6 +2593,11 @@
       <c r="AV9" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -2705,6 +2762,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. La lumière est claire. On referme le livre. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2929,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3096,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Des miettes dorment sur la table. On pose le ballon. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3263,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3430,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Un chat miaule une fois. On secoue le sable. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3597,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3764,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend le livre. Le sable est tiède. Le livre : une règle, on tourne une page. Rappeler. Une règle. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3959,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3891,7 +3988,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Nora pose un jeton rouge. Les chaussures font toc toc. On caresse le tissu. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose un jeton rouge. Les chaussures font toc toc. On caresse le tissu. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4029,6 +4126,12 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. Les chaussures font toc toc. On caresse le tissu. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4294,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4461,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. La couverture est douce. On tend la main. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4628,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4795,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Une cloche tinte au loin. On chante un petit air. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4962,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5129,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend la dînette. Un grillon chante. La dînette : une règle, on pose puis on sert. Papa rappelle la règle. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5189,6 +5322,11 @@
       <c r="AV25" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -5353,6 +5491,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. Le bois sent le chaud. On compte jusqu'à trois. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5658,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5825,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Une goutte tombe, ploc. On montre du doigt. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5992,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6159,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Le savon sent la fleur. On range la chaise. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6326,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6325,6 +6493,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pense au toboggan. Ici, une règle : on attend son tour pour la carte. Papa rappelle la règle. Nora attend. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6678,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Si on oublie, on peut la. ?</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6851,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Une règle. Rappeler. Nora a attendu. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7046,11 @@
         <v>8</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7213,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend les cubes. Un grillon chante. Nora empile. Une règle. Papa la rappelle une fois. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7408,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7239,7 +7437,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Nora pose un jeton rouge. Le tissu est tout doux. On range un objet. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose un jeton rouge. Le tissu est tout doux. On range un objet. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7377,6 +7575,12 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. Le tissu est tout doux. On range un objet. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7743,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7910,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Une cuillère tinte. On se tient la main. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8077,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8244,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Le sable est tiède. On dit merci. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8411,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8578,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend le livre. Le papier froisse, chut. Nora touche le papier. Une règle : doucement. Rappeler. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8537,6 +8771,11 @@
       <c r="AV45" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -8701,6 +8940,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. Un rire court, tout petit. On souffle doucement. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9107,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9274,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Le papier froisse, chut. On écoute jusqu'au bout. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9441,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9608,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. L'herbe chatouille le mollet. On attend son tour. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9775,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9942,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend la dînette. Une pomme sent le sucré. Une tasse. Une règle. Nora pose. Papa rappelle. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10137,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9887,7 +10166,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Nora pose un jeton rouge. Un pigeon roucoule. On sourit ensemble. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose un jeton rouge. Un pigeon roucoule. On sourit ensemble. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10025,6 +10304,12 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. Un pigeon roucoule. On sourit ensemble. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10472,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10639,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. La fenêtre vibre un peu. On pose les pieds par terre. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10806,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10973,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Le lait est froid dans le verre. On parle tout bas. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11140,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10997,6 +11307,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pense aux balançoires. Une règle : on parle tout bas. Papa la rappelle une fois. Nora chuchote. La règle. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Attendre, c'est une quoi ?</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|La règle dite. Nora l'a suivie. Papa a rappelé une fois. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>8</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend les cubes. Des miettes dorment sur la table. Les cubes tiennent. Une règle suivie. On peut la rappeler. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11885,6 +12220,11 @@
       <c r="AV65" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -12049,6 +12389,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. La corde du sac est rêche. On range les jouets. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Le savon mousse entre les doigts. On s'assoit un moment. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Un ruisseau chante. On respire, un, deux. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend le livre. Un nuage passe lentement. Le livre se ferme. Une règle. Rappeler. Nora a suivi. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13586,11 @@
           <t>prompt réécrit pour coller aux options</t>
         </is>
       </c>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13235,7 +13615,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Nora pose un jeton rouge. La laine gratte un peu. On referme le sac. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora range. Papa dit : c'est bien.</t>
+          <t>Nora pose un jeton rouge. La laine gratte un peu. On referme le sac. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13373,6 +13753,12 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. La laine gratte un peu. On referme le sac. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora range.
+papa|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13921,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14088,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Un pain croustille. On essuie une miette. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14255,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14422,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Le savon glisse. On met le doudou près. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14589,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14756,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Nora prend la dînette. Le tissu est tout doux. Nora range. Une règle simple. Papa l'a rappelée. Nora l'a suivie. On suit une règle. On peut la rappeler une fois.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14533,6 +14949,11 @@
       <c r="AV81" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
     </row>
@@ -14697,6 +15118,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton rouge. Une plume vole. On lace les chaussures. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15285,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15452,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton bleu. Le banc est lisse. On met le manteau. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15619,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15786,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Nora pose un jeton vert. Un grelot sonne. On boit une gorgée. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15953,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15976,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A10"/>
+  <dimension ref="A1:A11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15598,6 +16049,13 @@
       <c r="A10" t="inlineStr">
         <is>
           <t>ch3C3: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-JEU-005.xlsx
+++ b/stories/arbres/TREE-JEU-005.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Nora est dans le train, avec papa. Un petit jeu de cartes épaisses. Papa dit une règle : on attend, puis on pose une carte. Une règle. Nora attend. Nora pose. Papa la rappelle une fois, tout doux. Rappeler. Une règle. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre le bac à sable, le toboggan, ou les balançoires.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1685,6 +1692,7 @@
           <t>narrateur|Nora pense au bac à sable. La règle : on reste assis dans le train. Une règle. Papa la rappelle. Nora suit la règle dite. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1872,6 +1880,7 @@
           <t>narrateur|On suit une quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2043,6 +2052,7 @@
           <t>narrateur|Nora a suivi une règle. Papa a pu la rappeler. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2238,6 +2248,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2405,6 +2416,7 @@
           <t>narrateur|Nora prend les cubes. La corde du sac est rêche. Les cubes : une règle, un cube à la fois. Papa la rappelle. Nora suit. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2600,6 +2612,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2767,6 +2780,7 @@
           <t>narrateur|Nora pose un jeton rouge. La lumière est claire. On referme le livre. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2934,6 +2948,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3101,6 +3116,7 @@
           <t>narrateur|Nora pose un jeton bleu. Des miettes dorment sur la table. On pose le ballon. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3268,6 +3284,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3435,6 +3452,7 @@
           <t>narrateur|Nora pose un jeton vert. Un chat miaule une fois. On secoue le sable. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3602,6 +3620,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3769,6 +3788,7 @@
           <t>narrateur|Nora prend le livre. Le sable est tiède. Le livre : une règle, on tourne une page. Rappeler. Une règle. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3964,6 +3984,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4132,6 +4153,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4299,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
           <t>narrateur|Nora pose un jeton bleu. La couverture est douce. On tend la main. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4800,6 +4825,7 @@
           <t>narrateur|Nora pose un jeton vert. Une cloche tinte au loin. On chante un petit air. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4967,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5134,6 +5161,7 @@
           <t>narrateur|Nora prend la dînette. Un grillon chante. La dînette : une règle, on pose puis on sert. Papa rappelle la règle. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5329,6 +5357,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5496,6 +5525,7 @@
           <t>narrateur|Nora pose un jeton rouge. Le bois sent le chaud. On compte jusqu'à trois. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5663,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5830,6 +5861,7 @@
           <t>narrateur|Nora pose un jeton bleu. Une goutte tombe, ploc. On montre du doigt. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5997,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6164,6 +6197,7 @@
           <t>narrateur|Nora pose un jeton vert. Le savon sent la fleur. On range la chaise. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6331,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6498,6 +6533,7 @@
           <t>narrateur|Nora pense au toboggan. Ici, une règle : on attend son tour pour la carte. Papa rappelle la règle. Nora attend. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6685,6 +6721,7 @@
           <t>narrateur|Si on oublie, on peut la. ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6856,6 +6893,7 @@
           <t>narrateur|Une règle. Rappeler. Nora a attendu. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7051,6 +7089,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7218,6 +7257,7 @@
           <t>narrateur|Nora prend les cubes. Un grillon chante. Nora empile. Une règle. Papa la rappelle une fois. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7413,6 +7453,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Nora pose un jeton bleu. Une cuillère tinte. On se tient la main. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Nora pose un jeton vert. Le sable est tiède. On dit merci. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Nora prend le livre. Le papier froisse, chut. Nora touche le papier. Une règle : doucement. Rappeler. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Nora pose un jeton rouge. Un rire court, tout petit. On souffle doucement. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Nora pose un jeton bleu. Le papier froisse, chut. On écoute jusqu'au bout. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>narrateur|Nora pose un jeton vert. L'herbe chatouille le mollet. On attend son tour. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|Nora prend la dînette. Une pomme sent le sucré. Une tasse. Une règle. Nora pose. Papa rappelle. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10310,6 +10367,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10477,6 +10535,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10644,6 +10703,7 @@
           <t>narrateur|Nora pose un jeton bleu. La fenêtre vibre un peu. On pose les pieds par terre. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10811,6 +10871,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10978,6 +11039,7 @@
           <t>narrateur|Nora pose un jeton vert. Le lait est froid dans le verre. On parle tout bas. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11145,6 +11207,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
           <t>narrateur|Nora pense aux balançoires. Une règle : on parle tout bas. Papa la rappelle une fois. Nora chuchote. La règle. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Attendre, c'est une quoi ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|La règle dite. Nora l'a suivie. Papa a rappelé une fois. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Nora prend les cubes. Des miettes dorment sur la table. Les cubes tiennent. Une règle suivie. On peut la rappeler. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Nora pose un jeton rouge. La corde du sac est rêche. On range les jouets. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Nora pose un jeton bleu. Le savon mousse entre les doigts. On s'assoit un moment. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Nora pose un jeton vert. Un ruisseau chante. On respire, un, deux. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Nora prend le livre. Un nuage passe lentement. Le livre se ferme. Une règle. Rappeler. Nora a suivi. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13759,6 +13836,7 @@
 papa|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13926,6 +14004,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14093,6 +14172,7 @@
           <t>narrateur|Nora pose un jeton bleu. Un pain croustille. On essuie une miette. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. On souffle. Nora sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14260,6 +14340,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14427,6 +14508,7 @@
           <t>narrateur|Nora pose un jeton vert. Le savon glisse. On met le doudou près. On a suivi une règle. On a pu la rappeler. Le train continue. On suit une règle. On peut la rappeler une fois. Nora prend la main de papa.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14594,6 +14676,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14761,6 +14844,7 @@
           <t>narrateur|Nora prend la dînette. Le tissu est tout doux. Nora range. Une règle simple. Papa l'a rappelée. Nora l'a suivie. On suit une règle. On peut la rappeler une fois.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14956,6 +15040,7 @@
           <t>narrateur|On peut prendre rouge, bleu, ou vert.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15123,6 +15208,7 @@
           <t>narrateur|Nora pose un jeton rouge. Une plume vole. On lace les chaussures. On a suivi une règle. On a pu la rappeler. On a attendu. On suit une règle. On peut la rappeler une fois. Nora dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15290,6 +15376,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15457,6 +15544,7 @@
           <t>narrateur|Nora pose un jeton bleu. Le banc est lisse. On met le manteau. On a suivi une règle. On a pu la rappeler. La voix était douce. On suit une règle. On peut la rappeler une fois. Papa serre Nora tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15624,6 +15712,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15791,6 +15880,7 @@
           <t>narrateur|Nora pose un jeton vert. Un grelot sonne. On boit une gorgée. On a suivi une règle. On a pu la rappeler. La carte est posée. On suit une règle. On peut la rappeler une fois. Maman n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15958,6 +16048,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15976,7 +16067,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A11"/>
+  <dimension ref="A1:A13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16056,6 +16147,20 @@
       <c r="A11" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16070,7 +16175,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16257,6 +16362,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
